--- a/student_assessment_forms/009_human_development_assessment--student_assessment_forms.xlsx
+++ b/student_assessment_forms/009_human_development_assessment--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,43 +515,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>student_assessment_form</t>
+          <t>overall_wellbeing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>student_assessment_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Overall well-being</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>How do you rate your overall well-being?</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>overall_wellbeing</t>
+          <t>growth_areas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>overall_wellbeing</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Growth areas</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>What are your growth areas?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,23 +569,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>growth_areas</t>
+          <t>well_being_goals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>growth_areas</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Well-being goals</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>What are your well-being goals?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,38 +601,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>well_being_goals</t>
+          <t>personal_goals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>well_being_goals</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Personal goals</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What are your personal goals?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>personal_goals</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>personal_goals</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Overall rating</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How would you rate your overall well-being?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,23 +650,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>overall_rating</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>overall_rating</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Any comments?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Your email address</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Your phone number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -745,43 +785,51 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Any additional comments?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Submitted by</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Your name</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_at</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Submitted at</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Date and time of submission</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>submitted_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Submitted time</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Time of submission</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -837,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_at_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Submitted At 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Date of submission</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>submitted_at_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Submitted At 3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Date of submission</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,205 +947,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>submitted_time_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Submitted Time 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Time of submission</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submitted_at</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,8 +986,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1015,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1032,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1049,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1066,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'emotional_stability'}</t>
+          <t>emotional_stability</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Emotional Stability'}</t>
+          <t>Emotional Stability</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1083,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'self-awareness'}</t>
+          <t>self-awareness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Self-awareness'}</t>
+          <t>Self-awareness</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1100,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'social_skills'}</t>
+          <t>social_skills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Social Skills'}</t>
+          <t>Social Skills</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1117,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'physical_health'}</t>
+          <t>physical_health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Health'}</t>
+          <t>Physical Health</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1134,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'mental_health'}</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Mental Health'}</t>
+          <t>Mental Health</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1151,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1168,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1185,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
